--- a/artfynd/A 24437-2024 artfynd.xlsx
+++ b/artfynd/A 24437-2024 artfynd.xlsx
@@ -1693,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120047169</v>
+        <v>120047135</v>
       </c>
       <c r="B11" t="n">
-        <v>91840</v>
+        <v>90712</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1705,25 +1705,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463702</v>
+        <v>463713</v>
       </c>
       <c r="R11" t="n">
-        <v>7096980</v>
+        <v>7096998</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120047135</v>
+        <v>120047169</v>
       </c>
       <c r="B12" t="n">
-        <v>90712</v>
+        <v>91840</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,25 +1807,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463713</v>
+        <v>463702</v>
       </c>
       <c r="R12" t="n">
-        <v>7096998</v>
+        <v>7096980</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>

--- a/artfynd/A 24437-2024 artfynd.xlsx
+++ b/artfynd/A 24437-2024 artfynd.xlsx
@@ -1693,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120047135</v>
+        <v>120047169</v>
       </c>
       <c r="B11" t="n">
-        <v>90712</v>
+        <v>91840</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1705,25 +1705,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463713</v>
+        <v>463702</v>
       </c>
       <c r="R11" t="n">
-        <v>7096998</v>
+        <v>7096980</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120047169</v>
+        <v>120047135</v>
       </c>
       <c r="B12" t="n">
-        <v>91840</v>
+        <v>90712</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,25 +1807,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463702</v>
+        <v>463713</v>
       </c>
       <c r="R12" t="n">
-        <v>7096980</v>
+        <v>7096998</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>

--- a/artfynd/A 24437-2024 artfynd.xlsx
+++ b/artfynd/A 24437-2024 artfynd.xlsx
@@ -1591,7 +1591,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120047210</v>
+        <v>120047169</v>
       </c>
       <c r="B10" t="n">
         <v>91840</v>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463701</v>
+        <v>463702</v>
       </c>
       <c r="R10" t="n">
-        <v>7096905</v>
+        <v>7096980</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1693,7 +1693,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120047169</v>
+        <v>120047210</v>
       </c>
       <c r="B11" t="n">
         <v>91840</v>
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463702</v>
+        <v>463701</v>
       </c>
       <c r="R11" t="n">
-        <v>7096980</v>
+        <v>7096905</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>

--- a/artfynd/A 24437-2024 artfynd.xlsx
+++ b/artfynd/A 24437-2024 artfynd.xlsx
@@ -1591,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120047169</v>
+        <v>120047135</v>
       </c>
       <c r="B10" t="n">
-        <v>91840</v>
+        <v>90730</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1603,25 +1603,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463702</v>
+        <v>463713</v>
       </c>
       <c r="R10" t="n">
-        <v>7096980</v>
+        <v>7096998</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1693,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120047210</v>
+        <v>120047169</v>
       </c>
       <c r="B11" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463701</v>
+        <v>463702</v>
       </c>
       <c r="R11" t="n">
-        <v>7096905</v>
+        <v>7096980</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120047135</v>
+        <v>120047210</v>
       </c>
       <c r="B12" t="n">
-        <v>90712</v>
+        <v>91858</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,25 +1807,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463713</v>
+        <v>463701</v>
       </c>
       <c r="R12" t="n">
-        <v>7096998</v>
+        <v>7096905</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>

--- a/artfynd/A 24437-2024 artfynd.xlsx
+++ b/artfynd/A 24437-2024 artfynd.xlsx
@@ -1591,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120047135</v>
+        <v>120047210</v>
       </c>
       <c r="B10" t="n">
-        <v>90730</v>
+        <v>91858</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1603,25 +1603,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463713</v>
+        <v>463701</v>
       </c>
       <c r="R10" t="n">
-        <v>7096998</v>
+        <v>7096905</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120047210</v>
+        <v>120047135</v>
       </c>
       <c r="B12" t="n">
-        <v>91858</v>
+        <v>90730</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,25 +1807,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463701</v>
+        <v>463713</v>
       </c>
       <c r="R12" t="n">
-        <v>7096905</v>
+        <v>7096998</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>

--- a/artfynd/A 24437-2024 artfynd.xlsx
+++ b/artfynd/A 24437-2024 artfynd.xlsx
@@ -1693,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120047169</v>
+        <v>120047135</v>
       </c>
       <c r="B11" t="n">
-        <v>91858</v>
+        <v>90730</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1705,25 +1705,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463702</v>
+        <v>463713</v>
       </c>
       <c r="R11" t="n">
-        <v>7096980</v>
+        <v>7096998</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120047135</v>
+        <v>120047169</v>
       </c>
       <c r="B12" t="n">
-        <v>90730</v>
+        <v>91858</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,25 +1807,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463713</v>
+        <v>463702</v>
       </c>
       <c r="R12" t="n">
-        <v>7096998</v>
+        <v>7096980</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>

--- a/artfynd/A 24437-2024 artfynd.xlsx
+++ b/artfynd/A 24437-2024 artfynd.xlsx
@@ -1591,7 +1591,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120047210</v>
+        <v>120047169</v>
       </c>
       <c r="B10" t="n">
         <v>91858</v>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463701</v>
+        <v>463702</v>
       </c>
       <c r="R10" t="n">
-        <v>7096905</v>
+        <v>7096980</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1795,7 +1795,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120047169</v>
+        <v>120047210</v>
       </c>
       <c r="B12" t="n">
         <v>91858</v>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463702</v>
+        <v>463701</v>
       </c>
       <c r="R12" t="n">
-        <v>7096980</v>
+        <v>7096905</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>

--- a/artfynd/A 24437-2024 artfynd.xlsx
+++ b/artfynd/A 24437-2024 artfynd.xlsx
@@ -1693,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120047135</v>
+        <v>120047210</v>
       </c>
       <c r="B11" t="n">
-        <v>90730</v>
+        <v>91858</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1705,25 +1705,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463713</v>
+        <v>463701</v>
       </c>
       <c r="R11" t="n">
-        <v>7096998</v>
+        <v>7096905</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120047210</v>
+        <v>120047135</v>
       </c>
       <c r="B12" t="n">
-        <v>91858</v>
+        <v>90730</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,25 +1807,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463701</v>
+        <v>463713</v>
       </c>
       <c r="R12" t="n">
-        <v>7096905</v>
+        <v>7096998</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
